--- a/Excel/Global/Test/Test -- 测试用.xlsx
+++ b/Excel/Global/Test/Test -- 测试用.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\MRFramework\Excel\Global\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\MRFramework\Excel\Global\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C1DDFA-FCD8-4736-9EF7-B889C3A86BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DFBA33-830D-424C-AA71-102049E7BA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="1695" windowWidth="21945" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestConfig" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,26 +75,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BuildPosX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuildPosY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生成位置X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生成位置Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PrefabPath</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -115,6 +95,78 @@
   </si>
   <si>
     <t>是否是普通矿石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntArrayTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数组1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StringArrayTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数组2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1, 2, 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"测试1", "测试2", "测试3"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FloatArrayTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数组3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5, 2.0, 3.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.7, 3.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildPos1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildPos2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.7, 3.4, 8.9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -190,21 +242,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -494,720 +546,764 @@
     <col min="3" max="3" width="26.125" customWidth="1"/>
     <col min="4" max="4" width="59.5" customWidth="1"/>
     <col min="5" max="5" width="29.5" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="23.125" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="17.5" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="E1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="E2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="D4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="2">
         <v>30</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="7" t="b">
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="5">
+      <c r="F6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="5">
-        <v>30</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>5.76</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2.13</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>30</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>-3.4</v>
-      </c>
-      <c r="G7" s="5">
-        <v>-3.78</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
